--- a/AAII_Financials/Quarterly/AJIA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AJIA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
   <si>
     <t>AJIA</t>
   </si>
@@ -656,136 +656,140 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44834</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44651</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44561</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44469</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44286</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44196</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44104</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43921</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43738</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43646</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43555</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43373</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43190</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43100</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43008</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42916</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42825</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42735</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42643</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -793,14 +797,14 @@
         <v>5</v>
       </c>
       <c r="E8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3">
+        <v>100</v>
+      </c>
+      <c r="G8" s="3">
         <v>200</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
       <c r="H8" s="3">
         <v>0</v>
       </c>
@@ -823,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="O8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -850,10 +854,10 @@
         <v>0</v>
       </c>
       <c r="X8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z8" s="3">
         <v>0</v>
@@ -873,8 +877,11 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -885,11 +892,11 @@
         <v>0</v>
       </c>
       <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
         <v>200</v>
       </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
       <c r="H9" s="3">
         <v>0</v>
       </c>
@@ -905,17 +912,17 @@
       <c r="L9" s="3">
         <v>0</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>5</v>
+      <c r="M9" s="3">
+        <v>0</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3">
+        <v>0</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>5</v>
@@ -923,11 +930,11 @@
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S9" s="3">
-        <v>100</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>5</v>
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
+        <v>100</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>5</v>
@@ -935,20 +942,20 @@
       <c r="V9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W9" s="3">
-        <v>100</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>5</v>
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="3">
+        <v>100</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="3" t="s">
-        <v>5</v>
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>0</v>
       </c>
       <c r="AB9" s="3" t="s">
         <v>5</v>
@@ -962,8 +969,11 @@
       <c r="AE9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -971,10 +981,10 @@
         <v>5</v>
       </c>
       <c r="E10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
@@ -994,17 +1004,17 @@
       <c r="L10" s="3">
         <v>0</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
+      <c r="M10" s="3">
+        <v>0</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O10" s="3">
-        <v>100</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3">
+        <v>100</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
@@ -1012,32 +1022,32 @@
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3">
         <v>-100</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X10" s="3">
         <v>-100</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="3" t="s">
-        <v>5</v>
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>0</v>
       </c>
       <c r="AB10" s="3" t="s">
         <v>5</v>
@@ -1051,8 +1061,11 @@
       <c r="AE10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,31 +1279,34 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1306,17 +1326,17 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>5</v>
@@ -1324,11 +1344,11 @@
       <c r="V14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W14" s="3">
-        <v>100</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>5</v>
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
+        <v>100</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>5</v>
@@ -1339,8 +1359,8 @@
       <c r="AA14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1351,8 +1371,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1395,8 +1418,8 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>5</v>
+      <c r="Q15" s="3">
+        <v>0</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>5</v>
@@ -1416,11 +1439,11 @@
       <c r="W15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3" t="s">
-        <v>5</v>
+      <c r="X15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>5</v>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,25 +1496,26 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E17" s="3">
         <v>200</v>
       </c>
-      <c r="E17" s="3">
-        <v>100</v>
-      </c>
       <c r="F17" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G17" s="3">
         <v>300</v>
       </c>
       <c r="H17" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I17" s="3">
         <v>100</v>
@@ -1503,16 +1530,16 @@
         <v>100</v>
       </c>
       <c r="M17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="3">
         <v>100</v>
@@ -1524,25 +1551,25 @@
         <v>100</v>
       </c>
       <c r="T17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V17" s="3">
         <v>100</v>
       </c>
       <c r="W17" s="3">
+        <v>100</v>
+      </c>
+      <c r="X17" s="3">
         <v>200</v>
       </c>
-      <c r="X17" s="3">
-        <v>100</v>
-      </c>
       <c r="Y17" s="3">
         <v>100</v>
       </c>
       <c r="Z17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA17" s="3">
         <v>0</v>
@@ -1559,8 +1586,11 @@
       <c r="AE17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1568,16 +1598,16 @@
         <v>5</v>
       </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
         <v>-100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-300</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-100</v>
       </c>
       <c r="I18" s="3">
         <v>-100</v>
@@ -1592,16 +1622,16 @@
         <v>-100</v>
       </c>
       <c r="M18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
         <v>-100</v>
       </c>
-      <c r="O18" s="3">
-        <v>100</v>
-      </c>
       <c r="P18" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="Q18" s="3">
         <v>-100</v>
@@ -1613,26 +1643,26 @@
         <v>-100</v>
       </c>
       <c r="T18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V18" s="3">
         <v>-100</v>
       </c>
       <c r="W18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X18" s="3">
         <v>-200</v>
       </c>
-      <c r="X18" s="3">
-        <v>0</v>
-      </c>
       <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-100</v>
       </c>
-      <c r="Z18" s="3">
-        <v>0</v>
-      </c>
       <c r="AA18" s="3">
         <v>0</v>
       </c>
@@ -1648,8 +1678,11 @@
       <c r="AE18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1714,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1720,29 +1754,29 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>100</v>
-      </c>
       <c r="Q20" s="3">
         <v>100</v>
       </c>
       <c r="R20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1770,8 +1804,11 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1779,28 +1816,28 @@
         <v>5</v>
       </c>
       <c r="E21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-100</v>
       </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
       <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
         <v>-300</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
       <c r="I21" s="3">
         <v>0</v>
       </c>
       <c r="J21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3">
         <v>-100</v>
       </c>
       <c r="L21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M21" s="3">
         <v>0</v>
@@ -1818,25 +1855,25 @@
         <v>0</v>
       </c>
       <c r="R21" s="3">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3">
         <v>-100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-200</v>
       </c>
-      <c r="T21" s="3">
-        <v>0</v>
-      </c>
       <c r="U21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V21" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="W21" s="3">
         <v>-100</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>5</v>
+      <c r="X21" s="3">
+        <v>-100</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>5</v>
@@ -1859,8 +1896,11 @@
       <c r="AE21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1948,37 +1988,40 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-100</v>
       </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
       <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
         <v>-300</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
       <c r="I23" s="3">
         <v>0</v>
       </c>
       <c r="J23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3">
         <v>-100</v>
       </c>
       <c r="L23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M23" s="3">
         <v>0</v>
@@ -1996,32 +2039,32 @@
         <v>0</v>
       </c>
       <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-200</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
       <c r="U23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V23" s="3">
+        <v>100</v>
+      </c>
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-200</v>
       </c>
-      <c r="X23" s="3">
-        <v>0</v>
-      </c>
       <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3">
         <v>-100</v>
       </c>
-      <c r="Z23" s="3">
-        <v>0</v>
-      </c>
       <c r="AA23" s="3">
         <v>0</v>
       </c>
@@ -2037,8 +2080,11 @@
       <c r="AE23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2126,8 +2172,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,37 +2264,40 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-100</v>
       </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
       <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>-300</v>
       </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
       <c r="I26" s="3">
         <v>0</v>
       </c>
       <c r="J26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3">
         <v>-100</v>
       </c>
       <c r="L26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M26" s="3">
         <v>0</v>
@@ -2263,32 +2315,32 @@
         <v>0</v>
       </c>
       <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
       <c r="U26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V26" s="3">
+        <v>100</v>
+      </c>
+      <c r="W26" s="3">
         <v>-100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-200</v>
       </c>
-      <c r="X26" s="3">
-        <v>0</v>
-      </c>
       <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3">
         <v>-100</v>
       </c>
-      <c r="Z26" s="3">
-        <v>0</v>
-      </c>
       <c r="AA26" s="3">
         <v>0</v>
       </c>
@@ -2304,37 +2356,40 @@
       <c r="AE26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-100</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
       <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>-200</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
       <c r="I27" s="3">
         <v>0</v>
       </c>
       <c r="J27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K27" s="3">
         <v>-100</v>
       </c>
       <c r="L27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M27" s="3">
         <v>0</v>
@@ -2352,32 +2407,32 @@
         <v>0</v>
       </c>
       <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
       <c r="U27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V27" s="3">
+        <v>100</v>
+      </c>
+      <c r="W27" s="3">
         <v>-100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-200</v>
       </c>
-      <c r="X27" s="3">
-        <v>0</v>
-      </c>
       <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-100</v>
       </c>
-      <c r="Z27" s="3">
-        <v>0</v>
-      </c>
       <c r="AA27" s="3">
         <v>0</v>
       </c>
@@ -2393,8 +2448,11 @@
       <c r="AE27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2816,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2788,29 +2858,29 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="Q32" s="3">
         <v>-100</v>
       </c>
       <c r="R32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -2838,37 +2908,40 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-100</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
       <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>-200</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
       <c r="I33" s="3">
         <v>0</v>
       </c>
       <c r="J33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K33" s="3">
         <v>-100</v>
       </c>
       <c r="L33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M33" s="3">
         <v>0</v>
@@ -2886,32 +2959,32 @@
         <v>0</v>
       </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-200</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V33" s="3">
+        <v>100</v>
+      </c>
+      <c r="W33" s="3">
         <v>-100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-200</v>
       </c>
-      <c r="X33" s="3">
-        <v>0</v>
-      </c>
       <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-100</v>
       </c>
-      <c r="Z33" s="3">
-        <v>0</v>
-      </c>
       <c r="AA33" s="3">
         <v>0</v>
       </c>
@@ -2927,8 +3000,11 @@
       <c r="AE33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,37 +3092,40 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-100</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
       <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>-200</v>
       </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
       <c r="I35" s="3">
         <v>0</v>
       </c>
       <c r="J35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K35" s="3">
         <v>-100</v>
       </c>
       <c r="L35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M35" s="3">
         <v>0</v>
@@ -3064,32 +3143,32 @@
         <v>0</v>
       </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-200</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V35" s="3">
+        <v>100</v>
+      </c>
+      <c r="W35" s="3">
         <v>-100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-200</v>
       </c>
-      <c r="X35" s="3">
-        <v>0</v>
-      </c>
       <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-100</v>
       </c>
-      <c r="Z35" s="3">
-        <v>0</v>
-      </c>
       <c r="AA35" s="3">
         <v>0</v>
       </c>
@@ -3105,102 +3184,108 @@
       <c r="AE35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44834</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44651</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44561</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44469</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44286</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44196</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44104</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43921</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43738</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43646</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43555</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43373</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43190</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43100</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43008</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42916</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42825</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42735</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42643</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,8 +3351,9 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3277,13 +3364,13 @@
         <v>0</v>
       </c>
       <c r="F41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G41" s="3">
         <v>100</v>
       </c>
       <c r="H41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I41" s="3">
         <v>0</v>
@@ -3354,8 +3441,11 @@
       <c r="AE41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,8 +3533,11 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3455,10 +3548,10 @@
         <v>0</v>
       </c>
       <c r="F43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H43" s="3">
         <v>0</v>
@@ -3466,11 +3559,11 @@
       <c r="I43" s="3">
         <v>0</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -3484,8 +3577,8 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>5</v>
+      <c r="P43" s="3">
+        <v>0</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>5</v>
@@ -3493,8 +3586,8 @@
       <c r="R43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -3514,8 +3607,8 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>5</v>
+      <c r="Z43" s="3">
+        <v>0</v>
       </c>
       <c r="AA43" s="3" t="s">
         <v>5</v>
@@ -3523,17 +3616,20 @@
       <c r="AB43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD43" s="3" t="s">
-        <v>5</v>
+      <c r="AC43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD43" s="3">
+        <v>0</v>
       </c>
       <c r="AE43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3621,8 +3717,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3630,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3">
         <v>100</v>
@@ -3666,7 +3765,7 @@
         <v>100</v>
       </c>
       <c r="Q45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -3710,22 +3809,25 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E46" s="3">
+        <v>100</v>
+      </c>
+      <c r="F46" s="3">
         <v>200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>300</v>
-      </c>
-      <c r="G46" s="3">
-        <v>200</v>
       </c>
       <c r="H46" s="3">
         <v>200</v>
@@ -3734,7 +3836,7 @@
         <v>200</v>
       </c>
       <c r="J46" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K46" s="3">
         <v>100</v>
@@ -3755,7 +3857,7 @@
         <v>100</v>
       </c>
       <c r="Q46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R46" s="3">
         <v>0</v>
@@ -3799,8 +3901,11 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3888,8 +3993,11 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3953,8 +4061,8 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>5</v>
+      <c r="X48" s="3">
+        <v>0</v>
       </c>
       <c r="Y48" s="3" t="s">
         <v>5</v>
@@ -3965,8 +4073,8 @@
       <c r="AA48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB48" s="3">
-        <v>0</v>
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC48" s="3">
         <v>0</v>
@@ -3977,13 +4085,16 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
         <v>5000</v>
@@ -3995,7 +4106,7 @@
         <v>5000</v>
       </c>
       <c r="H49" s="3">
-        <v>100</v>
+        <v>5000</v>
       </c>
       <c r="I49" s="3">
         <v>100</v>
@@ -4003,8 +4114,8 @@
       <c r="J49" s="3">
         <v>100</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>5</v>
+      <c r="K49" s="3">
+        <v>100</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>5</v>
@@ -4021,8 +4132,8 @@
       <c r="P49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -4039,17 +4150,17 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X49" s="3">
-        <v>100</v>
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y49" s="3">
         <v>100</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>5</v>
+      <c r="Z49" s="3">
+        <v>100</v>
       </c>
       <c r="AA49" s="3" t="s">
         <v>5</v>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4361,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,35 +4545,38 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>100</v>
+      </c>
+      <c r="E54" s="3">
         <v>5100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5300</v>
-      </c>
-      <c r="H54" s="3">
-        <v>300</v>
       </c>
       <c r="I54" s="3">
         <v>300</v>
       </c>
       <c r="J54" s="3">
+        <v>300</v>
+      </c>
+      <c r="K54" s="3">
         <v>200</v>
       </c>
-      <c r="K54" s="3">
-        <v>100</v>
-      </c>
       <c r="L54" s="3">
         <v>100</v>
       </c>
@@ -4467,7 +4593,7 @@
         <v>100</v>
       </c>
       <c r="Q54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R54" s="3">
         <v>0</v>
@@ -4488,14 +4614,14 @@
         <v>0</v>
       </c>
       <c r="X54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y54" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z54" s="3">
         <v>200</v>
       </c>
-      <c r="Z54" s="3">
-        <v>0</v>
-      </c>
       <c r="AA54" s="3">
         <v>0</v>
       </c>
@@ -4511,8 +4637,11 @@
       <c r="AE54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,22 +4707,23 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3">
         <v>400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>500</v>
-      </c>
-      <c r="G57" s="3">
-        <v>400</v>
       </c>
       <c r="H57" s="3">
         <v>400</v>
@@ -4601,25 +4732,25 @@
         <v>400</v>
       </c>
       <c r="J57" s="3">
+        <v>400</v>
+      </c>
+      <c r="K57" s="3">
         <v>300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O57" s="3">
-        <v>100</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>5</v>
+      <c r="O57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P57" s="3">
+        <v>100</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>5</v>
@@ -4633,8 +4764,8 @@
       <c r="T57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
+      <c r="U57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V57" s="3">
         <v>0</v>
@@ -4654,20 +4785,23 @@
       <c r="AA57" s="3">
         <v>0</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>5</v>
+      <c r="AB57" s="3">
+        <v>0</v>
       </c>
       <c r="AC57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4755,13 +4889,16 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="E59" s="3">
         <v>700</v>
@@ -4770,10 +4907,10 @@
         <v>700</v>
       </c>
       <c r="G59" s="3">
+        <v>700</v>
+      </c>
+      <c r="H59" s="3">
         <v>600</v>
-      </c>
-      <c r="H59" s="3">
-        <v>200</v>
       </c>
       <c r="I59" s="3">
         <v>200</v>
@@ -4782,10 +4919,10 @@
         <v>200</v>
       </c>
       <c r="K59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M59" s="3">
         <v>200</v>
@@ -4794,10 +4931,10 @@
         <v>200</v>
       </c>
       <c r="O59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q59" s="3">
         <v>200</v>
@@ -4806,20 +4943,20 @@
         <v>200</v>
       </c>
       <c r="S59" s="3">
+        <v>200</v>
+      </c>
+      <c r="T59" s="3">
         <v>400</v>
-      </c>
-      <c r="T59" s="3">
-        <v>300</v>
       </c>
       <c r="U59" s="3">
         <v>300</v>
       </c>
       <c r="V59" s="3">
+        <v>300</v>
+      </c>
+      <c r="W59" s="3">
         <v>200</v>
       </c>
-      <c r="W59" s="3">
-        <v>100</v>
-      </c>
       <c r="X59" s="3">
         <v>100</v>
       </c>
@@ -4827,7 +4964,7 @@
         <v>100</v>
       </c>
       <c r="Z59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA59" s="3">
         <v>0</v>
@@ -4844,37 +4981,40 @@
       <c r="AE59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E60" s="3">
         <v>1100</v>
       </c>
       <c r="F60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G60" s="3">
         <v>1200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1000</v>
-      </c>
-      <c r="H60" s="3">
-        <v>600</v>
       </c>
       <c r="I60" s="3">
         <v>600</v>
       </c>
       <c r="J60" s="3">
+        <v>600</v>
+      </c>
+      <c r="K60" s="3">
         <v>500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>300</v>
-      </c>
-      <c r="L60" s="3">
-        <v>200</v>
       </c>
       <c r="M60" s="3">
         <v>200</v>
@@ -4895,20 +5035,20 @@
         <v>200</v>
       </c>
       <c r="S60" s="3">
+        <v>200</v>
+      </c>
+      <c r="T60" s="3">
         <v>400</v>
-      </c>
-      <c r="T60" s="3">
-        <v>300</v>
       </c>
       <c r="U60" s="3">
         <v>300</v>
       </c>
       <c r="V60" s="3">
+        <v>300</v>
+      </c>
+      <c r="W60" s="3">
         <v>200</v>
       </c>
-      <c r="W60" s="3">
-        <v>100</v>
-      </c>
       <c r="X60" s="3">
         <v>100</v>
       </c>
@@ -4916,7 +5056,7 @@
         <v>100</v>
       </c>
       <c r="Z60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA60" s="3">
         <v>0</v>
@@ -4933,8 +5073,11 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5022,8 +5165,11 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,37 +5533,40 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>300</v>
-      </c>
-      <c r="L66" s="3">
-        <v>200</v>
       </c>
       <c r="M66" s="3">
         <v>200</v>
@@ -5429,20 +5587,20 @@
         <v>200</v>
       </c>
       <c r="S66" s="3">
+        <v>200</v>
+      </c>
+      <c r="T66" s="3">
         <v>400</v>
-      </c>
-      <c r="T66" s="3">
-        <v>300</v>
       </c>
       <c r="U66" s="3">
         <v>300</v>
       </c>
       <c r="V66" s="3">
+        <v>300</v>
+      </c>
+      <c r="W66" s="3">
         <v>200</v>
       </c>
-      <c r="W66" s="3">
-        <v>100</v>
-      </c>
       <c r="X66" s="3">
         <v>100</v>
       </c>
@@ -5450,7 +5608,7 @@
         <v>100</v>
       </c>
       <c r="Z66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA66" s="3">
         <v>0</v>
@@ -5467,8 +5625,11 @@
       <c r="AE66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,37 +6027,40 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1200</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-1100</v>
       </c>
       <c r="G72" s="3">
         <v>-1100</v>
       </c>
       <c r="H72" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I72" s="3">
         <v>-1000</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-900</v>
       </c>
       <c r="J72" s="3">
         <v>-900</v>
       </c>
       <c r="K72" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L72" s="3">
         <v>-800</v>
-      </c>
-      <c r="L72" s="3">
-        <v>-700</v>
       </c>
       <c r="M72" s="3">
         <v>-700</v>
@@ -5895,7 +6069,7 @@
         <v>-700</v>
       </c>
       <c r="O72" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="P72" s="3">
         <v>-600</v>
@@ -5904,37 +6078,37 @@
         <v>-600</v>
       </c>
       <c r="R72" s="3">
+        <v>-600</v>
+      </c>
+      <c r="S72" s="3">
         <v>-700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-300</v>
-      </c>
-      <c r="X72" s="3">
-        <v>-200</v>
       </c>
       <c r="Y72" s="3">
         <v>-200</v>
       </c>
       <c r="Z72" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AA72" s="3">
         <v>-100</v>
       </c>
       <c r="AB72" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC72" s="3">
         <v>0</v>
@@ -5945,8 +6119,11 @@
       <c r="AE72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,37 +6395,40 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E76" s="3">
         <v>4100</v>
-      </c>
-      <c r="E76" s="3">
-        <v>4300</v>
       </c>
       <c r="F76" s="3">
         <v>4300</v>
       </c>
       <c r="G76" s="3">
+        <v>4300</v>
+      </c>
+      <c r="H76" s="3">
         <v>4400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-400</v>
-      </c>
-      <c r="I76" s="3">
-        <v>-300</v>
       </c>
       <c r="J76" s="3">
         <v>-300</v>
       </c>
       <c r="K76" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L76" s="3">
         <v>-200</v>
-      </c>
-      <c r="L76" s="3">
-        <v>-100</v>
       </c>
       <c r="M76" s="3">
         <v>-100</v>
@@ -6251,35 +6437,35 @@
         <v>-100</v>
       </c>
       <c r="O76" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P76" s="3">
         <v>0</v>
       </c>
       <c r="Q76" s="3">
+        <v>0</v>
+      </c>
+      <c r="R76" s="3">
         <v>-100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-300</v>
-      </c>
-      <c r="U76" s="3">
-        <v>-200</v>
       </c>
       <c r="V76" s="3">
         <v>-200</v>
       </c>
       <c r="W76" s="3">
+        <v>-200</v>
+      </c>
+      <c r="X76" s="3">
         <v>-100</v>
       </c>
-      <c r="X76" s="3">
-        <v>0</v>
-      </c>
       <c r="Y76" s="3">
         <v>0</v>
       </c>
@@ -6301,8 +6487,11 @@
       <c r="AE76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,131 +6579,137 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44834</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44651</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44561</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44469</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44286</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44196</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44104</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43921</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43738</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43646</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43555</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43373</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43190</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43100</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43008</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42916</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42825</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42735</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42643</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-100</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
       <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>-200</v>
       </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
       <c r="I81" s="3">
         <v>0</v>
       </c>
       <c r="J81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K81" s="3">
         <v>-100</v>
       </c>
       <c r="L81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M81" s="3">
         <v>0</v>
@@ -6532,32 +6727,32 @@
         <v>0</v>
       </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-200</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V81" s="3">
+        <v>100</v>
+      </c>
+      <c r="W81" s="3">
         <v>-100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-200</v>
       </c>
-      <c r="X81" s="3">
-        <v>0</v>
-      </c>
       <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-100</v>
       </c>
-      <c r="Z81" s="3">
-        <v>0</v>
-      </c>
       <c r="AA81" s="3">
         <v>0</v>
       </c>
@@ -6573,8 +6768,11 @@
       <c r="AE81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6671,8 +6870,8 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>5</v>
+      <c r="X83" s="3">
+        <v>0</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>5</v>
@@ -6683,8 +6882,8 @@
       <c r="AA83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB83" s="3">
-        <v>0</v>
+      <c r="AB83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC83" s="3">
         <v>0</v>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,8 +7354,11 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7149,13 +7366,13 @@
         <v>0</v>
       </c>
       <c r="E89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F89" s="3">
         <v>-100</v>
       </c>
       <c r="G89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H89" s="3">
         <v>0</v>
@@ -7164,11 +7381,11 @@
         <v>0</v>
       </c>
       <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>-100</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
       <c r="L89" s="3">
         <v>0</v>
       </c>
@@ -7188,26 +7405,26 @@
         <v>0</v>
       </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>200</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
         <v>-100</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3">
         <v>0</v>
       </c>
@@ -7229,8 +7446,11 @@
       <c r="AE89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7482,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7351,8 +7572,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,8 +7756,11 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7544,19 +7774,19 @@
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
+      <c r="K94" s="3">
+        <v>0</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>5</v>
@@ -7573,8 +7803,8 @@
       <c r="P94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -7618,8 +7848,11 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,8 +8250,11 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8019,22 +8265,22 @@
         <v>0</v>
       </c>
       <c r="F100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3">
         <v>100</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
       <c r="J100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -8055,25 +8301,25 @@
         <v>0</v>
       </c>
       <c r="R100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>100</v>
+      </c>
+      <c r="T100" s="3">
         <v>300</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>-100</v>
       </c>
-      <c r="V100" s="3">
-        <v>100</v>
-      </c>
       <c r="W100" s="3">
         <v>100</v>
       </c>
       <c r="X100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y100" s="3">
         <v>0</v>
@@ -8096,8 +8342,11 @@
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8149,20 +8398,20 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
+      <c r="T101" s="3">
+        <v>0</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="V101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>5</v>
+      <c r="X101" s="3">
+        <v>0</v>
       </c>
       <c r="Y101" s="3" t="s">
         <v>5</v>
@@ -8173,8 +8422,8 @@
       <c r="AA101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
+      <c r="AB101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC101" s="3">
         <v>0</v>
@@ -8185,8 +8434,11 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8194,11 +8446,11 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
         <v>0</v>
       </c>
@@ -8272,6 +8524,9 @@
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>0</v>
       </c>
     </row>
